--- a/subat/ozdilekteyim-subat-2026-arama-talebi.xlsx
+++ b/subat/ozdilekteyim-subat-2026-arama-talebi.xlsx
@@ -3441,17 +3441,21 @@
         <v>0.4944649446494465</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.4838709677419355</v>
+        <v>-0.5961538461538461</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.4482758620689655</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr"/>
+        <v>-0.475</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>bere modelleri</t>
+        </is>
+      </c>
       <c r="M54" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
@@ -19090,165 +19094,169 @@
           <t>bere</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>bere modelleri</t>
+        </is>
+      </c>
       <c r="C54" s="3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E54" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="H54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I54" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I54" s="3" t="n">
+      <c r="J54" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="S54" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J54" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L54" s="3" t="n">
+      <c r="T54" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M54" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="N54" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="O54" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P54" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q54" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="R54" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="S54" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="T54" s="3" t="n">
-        <v>27</v>
-      </c>
       <c r="U54" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AA54" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB54" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AC54" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD54" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AE54" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF54" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG54" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AH54" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AJ54" s="3" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AL54" s="3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AM54" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AN54" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AO54" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AP54" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AQ54" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR54" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="AS54" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT54" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU54" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AV54" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="AW54" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="AX54" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="AY54" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ54" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BA54" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB54" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="AP54" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ54" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="AR54" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS54" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AT54" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="AU54" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="AV54" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="AW54" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX54" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="AY54" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="AZ54" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA54" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB54" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="BC54" s="3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">

--- a/subat/ozdilekteyim-subat-2026-arama-talebi.xlsx
+++ b/subat/ozdilekteyim-subat-2026-arama-talebi.xlsx
@@ -10140,267 +10140,267 @@
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>23 Şub 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>23 Şubat - 1 Mart 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>2 Mar 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>2-8 Mart 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>9 Mar 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>9-15 Mart 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>16 Mar 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>16-22 Mart 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>23 Mar 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>23-29 Mart 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>30 Mar 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>30 Mart - 5 Nisan 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>6 Nis 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>6-12 Nisan 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>13 Nis 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>13-19 Nisan 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>20 Nis 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>20-26 Nisan 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>27 Nis 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>27 Nisan - 3 Mayıs 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>4 May 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>4-10 Mayıs 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>11 May 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>11-17 Mayıs 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
         <is>
-          <t>18 May 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>18-24 Mayıs 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="P1" s="8" t="inlineStr">
         <is>
-          <t>25 May 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>25-31 Mayıs 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>1 Haz 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>1-7 Haziran 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="R1" s="8" t="inlineStr">
         <is>
-          <t>8 Haz 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>8-14 Haziran 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="S1" s="8" t="inlineStr">
         <is>
-          <t>15 Haz 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>15-21 Haziran 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="T1" s="8" t="inlineStr">
         <is>
-          <t>22 Haz 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>22-28 Haziran 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="U1" s="8" t="inlineStr">
         <is>
-          <t>29 Haz 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>29 Haziran - 5 Temmuz 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>6 Tem 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>6-12 Temmuz 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>13 Tem 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>13-19 Temmuz 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
         <is>
-          <t>20 Tem 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>20-26 Temmuz 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="Y1" s="8" t="inlineStr">
         <is>
-          <t>27 Tem 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>27 Temmuz - 2 Ağustos 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="Z1" s="8" t="inlineStr">
         <is>
-          <t>3 Ağu 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>3-9 Ağustos 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AA1" s="8" t="inlineStr">
         <is>
-          <t>10 Ağu 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>10-16 Ağustos 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AB1" s="8" t="inlineStr">
         <is>
-          <t>17 Ağu 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>17-23 Ağustos 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AC1" s="8" t="inlineStr">
         <is>
-          <t>24 Ağu 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>24-30 Ağustos 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AD1" s="8" t="inlineStr">
         <is>
-          <t>31 Ağu 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>31 Ağustos - 6 Eylül 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AE1" s="8" t="inlineStr">
         <is>
-          <t>7 Eyl 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>7-13 Eylül 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AF1" s="8" t="inlineStr">
         <is>
-          <t>14 Eyl 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>14-20 Eylül 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AG1" s="8" t="inlineStr">
         <is>
-          <t>21 Eyl 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>21-27 Eylül 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AH1" s="8" t="inlineStr">
         <is>
-          <t>28 Eyl 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>28 Eylül - 4 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AI1" s="8" t="inlineStr">
         <is>
-          <t>5 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>5-11 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AJ1" s="8" t="inlineStr">
         <is>
-          <t>12 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>12-18 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AK1" s="8" t="inlineStr">
         <is>
-          <t>19 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>19-25 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AL1" s="8" t="inlineStr">
         <is>
-          <t>26 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>26 Ekim - 1 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AM1" s="8" t="inlineStr">
         <is>
-          <t>2 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>2-8 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AN1" s="8" t="inlineStr">
         <is>
-          <t>9 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>9-15 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AO1" s="8" t="inlineStr">
         <is>
-          <t>16 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>16-22 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AP1" s="8" t="inlineStr">
         <is>
-          <t>23 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>23-29 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AQ1" s="8" t="inlineStr">
         <is>
-          <t>30 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>30 Kasım - 6 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AR1" s="8" t="inlineStr">
         <is>
-          <t>7 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>7-13 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AS1" s="8" t="inlineStr">
         <is>
-          <t>14 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>14-20 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AT1" s="8" t="inlineStr">
         <is>
-          <t>21 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>21-27 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AU1" s="8" t="inlineStr">
         <is>
-          <t>28 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>28 Aralık 2025 - 3 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AV1" s="8" t="inlineStr">
         <is>
-          <t>4 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>4-10 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AW1" s="8" t="inlineStr">
         <is>
-          <t>11 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>11-17 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AX1" s="8" t="inlineStr">
         <is>
-          <t>18 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>18-24 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AY1" s="8" t="inlineStr">
         <is>
-          <t>25 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>25-31 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AZ1" s="8" t="inlineStr">
         <is>
-          <t>1 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>1-7 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="BA1" s="8" t="inlineStr">
         <is>
-          <t>8 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>8-14 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="BB1" s="8" t="inlineStr">
         <is>
-          <t>15 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>15-21 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="BC1" s="8" t="inlineStr">
         <is>
-          <t>22 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>22-28 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
     </row>
